--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-678027</t>
+          <t>I-265080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.0618934</t>
+          <t>-13.9235642</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.4188464</t>
+          <t>-70.5132752</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-690176</t>
+          <t>I-224216</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,25 +560,1013 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>-13.9928216</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-70.4567585</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I-690176</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-14.0611789</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>-70.4184519</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I-224196</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-13.9934708</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-70.4577013</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-265101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-13.9244771</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-70.5168853</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-224200</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-13.9819131</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-70.4590291</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-188395</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-14.0672359</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-70.4363707</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Avenida Puno / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-265082</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-13.9209973</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-70.514315</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-224228</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-13.9906597</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-70.4597542</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-224226</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-13.9962792</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-70.4580073</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-224224</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-13.9954344</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-70.4570668</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-224223</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-13.9943063</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-70.455861</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-224222</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-13.991363</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-70.4582221</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-224220</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-13.9928814</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-70.4603819</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-224217</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-13.9944704</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-70.4592498</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-265088</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-13.9199205</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-70.5141109</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-265095</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-13.9278883</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-70.5119927</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-399649</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-14.062056</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-70.4342347</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Carretera Interoceánica Puno - Madre de Dios / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-224211</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-13.9920655</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-70.4574892</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-224207</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-13.995311</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-70.4586844</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-224204</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-13.994734</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-70.4578287</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>210301</t>
         </is>

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1572,6 +1572,266 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-188397</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-14.0693633</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-70.4322359</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jirón Alfonso Ugarte / Jirón Inambari</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-224197</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-13.9920277</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-70.4592319</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-265097</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-13.9410329</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-70.5028401</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-265096</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-13.9268294</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-70.5126784</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-265086</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-13.9226133</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-70.5140101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -1610,7 +1610,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jirón Alfonso Ugarte / Jirón Inambari</t>
+          <t>Jirón Alfonso Ugarte / Jirón Bolognesi / Jirón Inambari</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-265080</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-13.9235642</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-224216</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-13.9928216</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-690176</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-14.0611789</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-224196</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-13.9934708</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-265101</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-13.9244771</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-224200</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-13.9819131</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-188395</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-14.0672359</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-265082</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-13.9209973</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-224228</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-13.9906597</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-224226</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-13.9962792</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-224224</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-13.9954344</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-224223</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-13.9943063</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-224222</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-13.991363</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-224220</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-13.9928814</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-224217</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-13.9944704</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-265088</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-13.9199205</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-265095</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-13.9278883</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-399649</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-14.062056</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-224211</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-13.9920655</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-224207</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-13.995311</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-224204</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-13.994734</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-188397</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-14.0693633</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-224197</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-13.9920277</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-265097</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-13.9410329</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-265096</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-13.9268294</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CARABAYA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MACUSANI</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-265086</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>210301</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CARABAYA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MACUSANI</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-13.9226133</t>
@@ -1824,11 +1694,6 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>210301</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.9235642</t>
+          <t>-14.06319951</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.5132752</t>
+          <t>-70.43199528</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.9928216</t>
+          <t>-14.07094706</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.4567585</t>
+          <t>-70.43134467</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.0611789</t>
+          <t>-14.06863515</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.4184519</t>
+          <t>-70.42599806</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.9934708</t>
+          <t>-14.07180563</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.4577013</t>
+          <t>-70.43027447</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.9244771</t>
+          <t>-14.07071646</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.5168853</t>
+          <t>-70.42690812</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-14.0672359</t>
+          <t>-14.0688589</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.4363707</t>
+          <t>-70.42702803</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Puno / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.9209973</t>
+          <t>-14.06499216</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.514315</t>
+          <t>-70.43072391</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-13.9906597</t>
+          <t>-14.07168335</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.4597542</t>
+          <t>-70.42974071</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-13.9962792</t>
+          <t>-14.06993521</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.4580073</t>
+          <t>-70.43335761</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.9954344</t>
+          <t>-14.06654511</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.4570668</t>
+          <t>-70.43509032</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Revolución con calle sn 2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1008,17 +1008,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.9943063</t>
+          <t>-14.06749346</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.455861</t>
+          <t>-70.43407913</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Arica con calle sn</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.991363</t>
+          <t>-14.07227915</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.4582221</t>
+          <t>-70.42946176</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.9928814</t>
+          <t>-14.06941488</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.4603819</t>
+          <t>-70.42566436</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.9944704</t>
+          <t>-14.06298563</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.4592498</t>
+          <t>-70.43000893</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.9199205</t>
+          <t>-14.06310585</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.5141109</t>
+          <t>-70.43112624</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-13.9278883</t>
+          <t>-14.06777347</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.5119927</t>
+          <t>-70.42318154</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.062056</t>
+          <t>-14.07126004</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.4342347</t>
+          <t>-70.42569521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Carretera Interoceánica Puno - Madre de Dios / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-13.9920655</t>
+          <t>-14.0674849</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-70.4574892</t>
+          <t>-70.43469084</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Revolución con calle crucero</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-13.995311</t>
+          <t>-14.0655044</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-70.4586844</t>
+          <t>-70.43599154</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Revolución con calle sn 1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-13.9920277</t>
+          <t>-14.06846247</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-70.4592319</t>
+          <t>-70.43410864</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Revolución altura plaza manco capac</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-13.9410329</t>
+          <t>-14.06563503</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-70.5028401</t>
+          <t>-70.43391568</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-13.9268294</t>
+          <t>-14.06552293</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-70.5126784</t>
+          <t>-70.42339075</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-13.9226133</t>
+          <t>-14.06604328</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-70.5140101</t>
+          <t>-70.43020624</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">

--- a/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
+++ b/Intersecciones/excels/PUNO-CARABAYA-MACUSANI.xlsx
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-265080</t>
+          <t>I-690176</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.06319951</t>
+          <t>-14.06863515</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.43199528</t>
+          <t>-70.42599806</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-224216</t>
+          <t>I-399649</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-14.07094706</t>
+          <t>-14.07126004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.43134467</t>
+          <t>-70.42569521</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -580,17 +580,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-690176</t>
+          <t>I-265101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.06863515</t>
+          <t>-14.07071646</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.42599806</t>
+          <t>-70.42690812</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,17 +627,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-224196</t>
+          <t>I-265097</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-14.07180563</t>
+          <t>-14.06563503</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.43027447</t>
+          <t>-70.43391568</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-265101</t>
+          <t>I-265096</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-14.07071646</t>
+          <t>-14.06552293</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.42690812</t>
+          <t>-70.42339075</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-224200</t>
+          <t>I-265095</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.9819131</t>
+          <t>-14.06777347</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-70.4590291</t>
+          <t>-70.42318154</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-188395</t>
+          <t>I-265088</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-14.0688589</t>
+          <t>-14.06310585</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.42702803</t>
+          <t>-70.43112624</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-265082</t>
+          <t>I-265086</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-14.06499216</t>
+          <t>-14.06604328</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.43072391</t>
+          <t>-70.43020624</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-224228</t>
+          <t>I-265082</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-14.07168335</t>
+          <t>-14.06499216</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.42974071</t>
+          <t>-70.43072391</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-224226</t>
+          <t>I-265080</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-14.06993521</t>
+          <t>-14.06319951</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.43335761</t>
+          <t>-70.43199528</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-224224</t>
+          <t>I-224228</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-14.06654511</t>
+          <t>-14.07168335</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.43509032</t>
+          <t>-70.42974071</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Revolución con calle sn 2</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-224223</t>
+          <t>I-224226</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14.06749346</t>
+          <t>-14.06993521</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.43407913</t>
+          <t>-70.43335761</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle Arica con calle sn</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-224222</t>
+          <t>I-224224</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-14.07227915</t>
+          <t>-14.06654511</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.42946176</t>
+          <t>-70.43509032</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Revolución con calle sn 2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-224220</t>
+          <t>I-224223</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-14.06941488</t>
+          <t>-14.06749346</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.42566436</t>
+          <t>-70.43407913</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Arica con calle sn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-224217</t>
+          <t>I-224222</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-14.06298563</t>
+          <t>-14.07227915</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.43000893</t>
+          <t>-70.42946176</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-265088</t>
+          <t>I-224220</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-14.06310585</t>
+          <t>-14.06941488</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.43112624</t>
+          <t>-70.42566436</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-265095</t>
+          <t>I-224217</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-14.06777347</t>
+          <t>-14.06298563</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.42318154</t>
+          <t>-70.43000893</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-399649</t>
+          <t>I-224216</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-14.07126004</t>
+          <t>-14.07094706</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.42569521</t>
+          <t>-70.43134467</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-188397</t>
+          <t>I-224200</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-14.0693633</t>
+          <t>-13.9819131</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-70.4322359</t>
+          <t>-70.4590291</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jirón Alfonso Ugarte / Jirón Bolognesi / Jirón Inambari</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-265097</t>
+          <t>I-224196</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-14.06563503</t>
+          <t>-14.07180563</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-70.43391568</t>
+          <t>-70.43027447</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-265096</t>
+          <t>I-188397</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-14.06552293</t>
+          <t>-14.0693633</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-70.42339075</t>
+          <t>-70.4322359</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Alfonso Ugarte / Jirón Inambari</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-265086</t>
+          <t>I-188395</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-14.06604328</t>
+          <t>-14.0688589</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-70.43020624</t>
+          <t>-70.42702803</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
